--- a/Leader NHÓM 6/KS25_CNTT6_NGONNGULAPTRINHC_Nhóm6 (4)1 (1)1 1 (1) (1) (1) (1) (1) 1 1 (1) (2) (2) (1) (1).xlsx
+++ b/Leader NHÓM 6/KS25_CNTT6_NGONNGULAPTRINHC_Nhóm6 (4)1 (1)1 1 (1) (1) (1) (1) (1) 1 1 (1) (2) (2) (1) (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\RIKKEI\Leader NHÓM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF07AAC9-299E-4E31-A1E2-BE9C3D20BFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461697C9-6DDD-4316-B3E4-50E0CDB2046B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,10 +146,10 @@
     <t>https://github.com/nthuat256/NguyenThienThuat_B25DTCN132_IT103B_Session8_BTVN.git</t>
   </si>
   <si>
-    <t>https://github.com/hungyha882007/javascripss8.git</t>
-  </si>
-  <si>
-    <t>]https://github.com/trandaivu/Tr-n-i-V-_it103bk25_session8.git</t>
+    <t>Nhóm phó: Nguyễn Thiện Thuật</t>
+  </si>
+  <si>
+    <t>https://github.com/trandaivu/Tr-n-i-V-_it202k25_session1.git</t>
   </si>
 </sst>
 </file>
@@ -334,6 +334,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -351,9 +354,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -635,7 +635,7 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="45.21875" style="2" customWidth="1"/>
     <col min="3" max="3" width="23.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.21875" style="2" customWidth="1"/>
@@ -651,50 +651,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38.700000000000003" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="20.399999999999999">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22" t="s">
+      <c r="D3" s="23"/>
+      <c r="E3" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="23"/>
+      <c r="G3" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="22"/>
+      <c r="H3" s="23"/>
     </row>
     <row r="4" spans="1:14" ht="20.399999999999999">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:14" ht="20.399999999999999">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18"/>
+      <c r="A5" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="19"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -748,10 +750,10 @@
         <v>14</v>
       </c>
       <c r="D8" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>14</v>
@@ -765,9 +767,7 @@
       <c r="I8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="J8" s="1"/>
       <c r="M8" s="12" t="s">
         <v>14</v>
       </c>
@@ -786,10 +786,10 @@
         <v>14</v>
       </c>
       <c r="D9" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>14</v>
@@ -803,7 +803,7 @@
       <c r="I9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="J9" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M9" s="13" t="s">
@@ -824,10 +824,10 @@
         <v>14</v>
       </c>
       <c r="D10" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>14</v>
@@ -851,7 +851,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" ht="33.6">
       <c r="A11" s="8">
         <v>4</v>
       </c>
@@ -862,7 +862,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="9">
         <v>6</v>
@@ -900,10 +900,10 @@
         <v>14</v>
       </c>
       <c r="D12" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>14</v>
@@ -968,11 +968,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="J8" r:id="rId1" xr:uid="{1A678DB6-3B47-4C1F-8661-343A8957E70E}"/>
-    <hyperlink ref="J11" r:id="rId2" display="https://github.com/trandaivu/Tr-n-i-V-_it103Bk25_-session6.git" xr:uid="{4486C57A-4F9C-4925-854A-575AC92151CE}"/>
-    <hyperlink ref="J12" r:id="rId3" xr:uid="{6F3626D9-38DD-4618-ADA3-8A19DCEFBE27}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{25F1A0DE-EF02-420C-B4CB-F28532D1EFAF}"/>
-    <hyperlink ref="J9" r:id="rId5" xr:uid="{E7867661-8080-457D-A33E-F0FF26244D6C}"/>
+    <hyperlink ref="J11" r:id="rId1" xr:uid="{4486C57A-4F9C-4925-854A-575AC92151CE}"/>
+    <hyperlink ref="J12" r:id="rId2" xr:uid="{6F3626D9-38DD-4618-ADA3-8A19DCEFBE27}"/>
+    <hyperlink ref="J10" r:id="rId3" xr:uid="{25F1A0DE-EF02-420C-B4CB-F28532D1EFAF}"/>
+    <hyperlink ref="J9" r:id="rId4" xr:uid="{E7867661-8080-457D-A33E-F0FF26244D6C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
